--- a/artfynd/A 41327-2023 artfynd.xlsx
+++ b/artfynd/A 41327-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41327-2023 artfynd.xlsx
+++ b/artfynd/A 41327-2023 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117721899</v>
+        <v>117723645</v>
       </c>
       <c r="B5" t="n">
-        <v>79465</v>
+        <v>94242</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,34 +1059,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skuruhäll, Gstr</t>
+          <t>Skuruhäll (Skuruhäll), Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562633</v>
+        <v>562737</v>
       </c>
       <c r="R5" t="n">
-        <v>6719638</v>
+        <v>6719608</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117723645</v>
+        <v>117721899</v>
       </c>
       <c r="B6" t="n">
-        <v>94240</v>
+        <v>79467</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,34 +1161,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skuruhäll (Skuruhäll), Gstr</t>
+          <t>Skuruhäll, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562737</v>
+        <v>562633</v>
       </c>
       <c r="R6" t="n">
-        <v>6719608</v>
+        <v>6719638</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
